--- a/faculty_schedule_manuel_finals_timetable.xlsx
+++ b/faculty_schedule_manuel_finals_timetable.xlsx
@@ -109,601 +109,610 @@
     <t>GIDA 202</t>
   </si>
   <si>
+    <t>MAK 436</t>
+  </si>
+  <si>
+    <t>EEE 420</t>
+  </si>
+  <si>
+    <t>İNM 102</t>
+  </si>
+  <si>
+    <t>EEE 488</t>
+  </si>
+  <si>
+    <t>JEO 306</t>
+  </si>
+  <si>
+    <t>MAK 416</t>
+  </si>
+  <si>
+    <t>MAK 302</t>
+  </si>
+  <si>
+    <t>EEM 316</t>
+  </si>
+  <si>
+    <t>ÇEV 312</t>
+  </si>
+  <si>
+    <t>CSE 184</t>
+  </si>
+  <si>
+    <t>CSE 214</t>
+  </si>
+  <si>
+    <t>KPD 102</t>
+  </si>
+  <si>
+    <t>ÇEV 156</t>
+  </si>
+  <si>
+    <t>EEM 202</t>
+  </si>
+  <si>
+    <t>EEM 112</t>
+  </si>
+  <si>
+    <t>EEE 486</t>
+  </si>
+  <si>
+    <t>ÇEV 432</t>
+  </si>
+  <si>
+    <t>CSE 474</t>
+  </si>
+  <si>
+    <t>CSE 102T</t>
+  </si>
+  <si>
+    <t>EEM 204</t>
+  </si>
+  <si>
+    <t>GIDA 326</t>
+  </si>
+  <si>
+    <t>İNM 404</t>
+  </si>
+  <si>
+    <t>EEM 220</t>
+  </si>
+  <si>
+    <t>JEO 410</t>
+  </si>
+  <si>
+    <t>MAK 440</t>
+  </si>
+  <si>
+    <t>MAK 206</t>
+  </si>
+  <si>
+    <t>İNM 206</t>
+  </si>
+  <si>
+    <t>ÇEV 208</t>
+  </si>
+  <si>
+    <t>MAT 152</t>
+  </si>
+  <si>
+    <t>CSE 392</t>
+  </si>
+  <si>
+    <t>EEM 394</t>
+  </si>
+  <si>
+    <t>ÇEV 354</t>
+  </si>
+  <si>
+    <t>FİZ 174</t>
+  </si>
+  <si>
+    <t>İNM 352</t>
+  </si>
+  <si>
+    <t>GIDA 424</t>
+  </si>
+  <si>
+    <t>İNM 310</t>
+  </si>
+  <si>
+    <t>JEO 104</t>
+  </si>
+  <si>
+    <t>MAK 104</t>
+  </si>
+  <si>
+    <t>İNM 108</t>
+  </si>
+  <si>
+    <t>ÇEV 204</t>
+  </si>
+  <si>
+    <t>CSE 444</t>
+  </si>
+  <si>
+    <t>CSE 434</t>
+  </si>
+  <si>
+    <t>CSE 438</t>
+  </si>
+  <si>
+    <t>MAK 102</t>
+  </si>
+  <si>
+    <t>FİZ 168</t>
+  </si>
+  <si>
+    <t>EEM 374</t>
+  </si>
+  <si>
+    <t>ÇEV 440</t>
+  </si>
+  <si>
+    <t>FİZ 176</t>
+  </si>
+  <si>
+    <t>CSE 204</t>
+  </si>
+  <si>
+    <t>EEM 256</t>
+  </si>
+  <si>
+    <t>JEO 206</t>
+  </si>
+  <si>
+    <t>MAK 310</t>
+  </si>
+  <si>
+    <t>MAT 162</t>
+  </si>
+  <si>
+    <t>ÇEV 184</t>
+  </si>
+  <si>
+    <t>GIDA 104</t>
+  </si>
+  <si>
+    <t>CSE 332</t>
+  </si>
+  <si>
+    <t>ÇEV 252</t>
+  </si>
+  <si>
+    <t>EEM 110</t>
+  </si>
+  <si>
+    <t>CSE 206</t>
+  </si>
+  <si>
+    <t>CSE 122</t>
+  </si>
+  <si>
     <t>MAK 432</t>
   </si>
   <si>
-    <t>EEE 420</t>
-  </si>
-  <si>
-    <t>İNM 102</t>
-  </si>
-  <si>
-    <t>EEM 316</t>
-  </si>
-  <si>
-    <t>JEO 104</t>
-  </si>
-  <si>
-    <t>CSE 392</t>
-  </si>
-  <si>
-    <t>MAK 104</t>
-  </si>
-  <si>
-    <t>EEM 202</t>
-  </si>
-  <si>
-    <t>ÇEV 208</t>
-  </si>
-  <si>
-    <t>MAT 152</t>
-  </si>
-  <si>
-    <t>ÇEV 156</t>
-  </si>
-  <si>
-    <t>FİZ 168</t>
-  </si>
-  <si>
-    <t>EEM 112</t>
-  </si>
-  <si>
-    <t>EEE 486</t>
-  </si>
-  <si>
-    <t>ÇEV 432</t>
-  </si>
-  <si>
-    <t>CSE 474</t>
-  </si>
-  <si>
-    <t>CSE 102T</t>
-  </si>
-  <si>
-    <t>EEM 204</t>
-  </si>
-  <si>
-    <t>GIDA 424</t>
-  </si>
-  <si>
-    <t>MAK 436</t>
-  </si>
-  <si>
-    <t>İNM 310</t>
-  </si>
-  <si>
-    <t>EEE 488</t>
-  </si>
-  <si>
-    <t>JEO 206</t>
-  </si>
-  <si>
-    <t>KPD 102</t>
-  </si>
-  <si>
-    <t>MAK 206</t>
-  </si>
-  <si>
-    <t>İNM 206</t>
-  </si>
-  <si>
-    <t>ÇEV 312</t>
-  </si>
-  <si>
-    <t>CSE 214</t>
-  </si>
-  <si>
-    <t>GIDA 326</t>
-  </si>
-  <si>
-    <t>EEM 394</t>
-  </si>
-  <si>
-    <t>ÇEV 354</t>
-  </si>
-  <si>
-    <t>FİZ 174</t>
-  </si>
-  <si>
-    <t>İNM 352</t>
-  </si>
-  <si>
-    <t>İNM 404</t>
-  </si>
-  <si>
-    <t>EEM 220</t>
-  </si>
-  <si>
-    <t>JEO 306</t>
+    <t>EEM 106</t>
+  </si>
+  <si>
+    <t>JEO 406</t>
   </si>
   <si>
     <t>MAK 414</t>
   </si>
   <si>
-    <t>MAK 302</t>
-  </si>
-  <si>
-    <t>İNM 108</t>
-  </si>
-  <si>
-    <t>ÇEV 184</t>
-  </si>
-  <si>
-    <t>CSE 184</t>
-  </si>
-  <si>
-    <t>CSE 434</t>
-  </si>
-  <si>
-    <t>CSE 438</t>
-  </si>
-  <si>
-    <t>GIDA 104</t>
-  </si>
-  <si>
-    <t>FİZ 176</t>
-  </si>
-  <si>
-    <t>ÇEV 440</t>
-  </si>
-  <si>
-    <t>CSE 122</t>
-  </si>
-  <si>
-    <t>EEM 256</t>
-  </si>
-  <si>
-    <t>JEO 410</t>
-  </si>
-  <si>
-    <t>MAK 416</t>
-  </si>
-  <si>
-    <t>MAK 310</t>
-  </si>
-  <si>
-    <t>MAT 162</t>
-  </si>
-  <si>
-    <t>ÇEV 204</t>
-  </si>
-  <si>
-    <t>CSE 444</t>
-  </si>
-  <si>
-    <t>CSE 332</t>
-  </si>
-  <si>
-    <t>MAK 102</t>
-  </si>
-  <si>
-    <t>EEM 374</t>
-  </si>
-  <si>
-    <t>ÇEV 252</t>
-  </si>
-  <si>
-    <t>CSE 206</t>
-  </si>
-  <si>
-    <t>CSE 204</t>
-  </si>
-  <si>
-    <t>EEM 106</t>
+    <t>MAK 204</t>
+  </si>
+  <si>
+    <t>İNM 486</t>
+  </si>
+  <si>
+    <t>ÇEV 402</t>
+  </si>
+  <si>
+    <t>CSE 424</t>
+  </si>
+  <si>
+    <t>ÇEV 216</t>
+  </si>
+  <si>
+    <t>JEO 106</t>
+  </si>
+  <si>
+    <t>EEE 418</t>
+  </si>
+  <si>
+    <t>MAT 222</t>
+  </si>
+  <si>
+    <t>ÇEV 308</t>
+  </si>
+  <si>
+    <t>CSE 102L</t>
+  </si>
+  <si>
+    <t>GIDA 422</t>
+  </si>
+  <si>
+    <t>MAK 438</t>
+  </si>
+  <si>
+    <t>İNM 494</t>
+  </si>
+  <si>
+    <t>EEE 482</t>
   </si>
   <si>
     <t>JEO 204</t>
   </si>
   <si>
+    <t>MAK 362</t>
+  </si>
+  <si>
+    <t>İNM 202</t>
+  </si>
+  <si>
+    <t>ÇEV 108</t>
+  </si>
+  <si>
+    <t>CSE 348</t>
+  </si>
+  <si>
+    <t>MAK 202</t>
+  </si>
+  <si>
+    <t>EEE 432</t>
+  </si>
+  <si>
+    <t>ÇEV 202</t>
+  </si>
+  <si>
+    <t>CSE 222</t>
+  </si>
+  <si>
+    <t>GIDA 353</t>
+  </si>
+  <si>
+    <t>İNM 464</t>
+  </si>
+  <si>
+    <t>GIDA 354</t>
+  </si>
+  <si>
+    <t>JEO 312</t>
+  </si>
+  <si>
     <t>İNM 458</t>
   </si>
   <si>
-    <t>MAK 440</t>
-  </si>
-  <si>
-    <t>MAK 204</t>
-  </si>
-  <si>
-    <t>İNM 486</t>
-  </si>
-  <si>
-    <t>ÇEV 108</t>
-  </si>
-  <si>
-    <t>JEO 106</t>
-  </si>
-  <si>
-    <t>EEE 418</t>
-  </si>
-  <si>
-    <t>MAT 222</t>
-  </si>
-  <si>
-    <t>ÇEV 308</t>
-  </si>
-  <si>
-    <t>EEM 110</t>
-  </si>
-  <si>
-    <t>CSE 102L</t>
+    <t>EEM 304</t>
+  </si>
+  <si>
+    <t>İNM 304</t>
+  </si>
+  <si>
+    <t>ÇEV 404</t>
+  </si>
+  <si>
+    <t>MAK 304</t>
+  </si>
+  <si>
+    <t>EEM 206</t>
+  </si>
+  <si>
+    <t>ÇEV 102</t>
+  </si>
+  <si>
+    <t>MAK 112</t>
+  </si>
+  <si>
+    <t>CSE 382</t>
   </si>
   <si>
     <t>GIDA 106</t>
   </si>
   <si>
-    <t>MAK 438</t>
+    <t>MAK 458</t>
   </si>
   <si>
     <t>EEE 458</t>
   </si>
   <si>
-    <t>JEO 406</t>
-  </si>
-  <si>
-    <t>MAK 362</t>
-  </si>
-  <si>
-    <t>İNM 202</t>
-  </si>
-  <si>
-    <t>ÇEV 402</t>
-  </si>
-  <si>
-    <t>CSE 348</t>
-  </si>
-  <si>
-    <t>MAK 202</t>
-  </si>
-  <si>
-    <t>CSE 424</t>
-  </si>
-  <si>
-    <t>ÇEV 216</t>
-  </si>
-  <si>
-    <t>EEE 432</t>
-  </si>
-  <si>
-    <t>ÇEV 102</t>
-  </si>
-  <si>
-    <t>CSE 222</t>
+    <t>JEO 304</t>
+  </si>
+  <si>
+    <t>EEM 456</t>
+  </si>
+  <si>
+    <t>İNM 106</t>
+  </si>
+  <si>
+    <t>ÇEV 328</t>
+  </si>
+  <si>
+    <t>MAK 208</t>
+  </si>
+  <si>
+    <t>CSE 320</t>
+  </si>
+  <si>
+    <t>EEM 350</t>
+  </si>
+  <si>
+    <t>EEM 302</t>
+  </si>
+  <si>
+    <t>EEM 370</t>
+  </si>
+  <si>
+    <t>ÇEV 352</t>
+  </si>
+  <si>
+    <t>GIDA 252</t>
+  </si>
+  <si>
+    <t>İNM 466</t>
   </si>
   <si>
     <t>GIDA 207</t>
   </si>
   <si>
-    <t>İNM 494</t>
-  </si>
-  <si>
-    <t>EEE 482</t>
+    <t>JEO 404</t>
+  </si>
+  <si>
+    <t>CSE 408</t>
+  </si>
+  <si>
+    <t>İNM 214</t>
+  </si>
+  <si>
+    <t>ÇEV 416</t>
+  </si>
+  <si>
+    <t>MAK 106</t>
+  </si>
+  <si>
+    <t>CSE 328</t>
+  </si>
+  <si>
+    <t>EEM 208</t>
+  </si>
+  <si>
+    <t>MAK 356</t>
+  </si>
+  <si>
+    <t>GIDA 238</t>
   </si>
   <si>
     <t>JEO 208</t>
   </si>
   <si>
-    <t>EEM 456</t>
-  </si>
-  <si>
-    <t>İNM 304</t>
-  </si>
-  <si>
-    <t>EEM 304</t>
-  </si>
-  <si>
-    <t>ÇEV 328</t>
-  </si>
-  <si>
-    <t>MAK 304</t>
-  </si>
-  <si>
-    <t>EEM 206</t>
-  </si>
-  <si>
-    <t>ÇEV 202</t>
-  </si>
-  <si>
-    <t>MAK 112</t>
-  </si>
-  <si>
-    <t>CSE 382</t>
-  </si>
-  <si>
-    <t>GIDA 422</t>
-  </si>
-  <si>
-    <t>MAK 356</t>
-  </si>
-  <si>
-    <t>İNM 464</t>
-  </si>
-  <si>
-    <t>JEO 304</t>
+    <t>İNM 212</t>
+  </si>
+  <si>
+    <t>EEE 484</t>
   </si>
   <si>
     <t>İNM 210</t>
   </si>
   <si>
-    <t>ÇEV 404</t>
-  </si>
-  <si>
-    <t>MAK 106</t>
-  </si>
-  <si>
-    <t>CSE 320</t>
-  </si>
-  <si>
-    <t>EEM 350</t>
-  </si>
-  <si>
-    <t>EEM 302</t>
-  </si>
-  <si>
-    <t>EEM 370</t>
-  </si>
-  <si>
-    <t>ÇEV 352</t>
-  </si>
-  <si>
-    <t>GIDA 252</t>
+    <t>EEE 496</t>
+  </si>
+  <si>
+    <t>ÇEV 306</t>
+  </si>
+  <si>
+    <t>MAK 308</t>
+  </si>
+  <si>
+    <t>CSE 308</t>
+  </si>
+  <si>
+    <t>CSE 358</t>
+  </si>
+  <si>
+    <t>EEM 210</t>
+  </si>
+  <si>
+    <t>EEM 352</t>
+  </si>
+  <si>
+    <t>MAK 426</t>
+  </si>
+  <si>
+    <t>GIDA 450</t>
+  </si>
+  <si>
+    <t>GIDA 222</t>
+  </si>
+  <si>
+    <t>İNM 204</t>
+  </si>
+  <si>
+    <t>ÇEV 210</t>
+  </si>
+  <si>
+    <t>CSE 336</t>
+  </si>
+  <si>
+    <t>MAK 210</t>
+  </si>
+  <si>
+    <t>CSE 472</t>
+  </si>
+  <si>
+    <t>MAK 402</t>
+  </si>
+  <si>
+    <t>İNM 356</t>
+  </si>
+  <si>
+    <t>EEM 306</t>
+  </si>
+  <si>
+    <t>JEO 408</t>
+  </si>
+  <si>
+    <t>İNM 452</t>
+  </si>
+  <si>
+    <t>ÇEV 162</t>
+  </si>
+  <si>
+    <t>CSE 460</t>
+  </si>
+  <si>
+    <t>MAK 110</t>
+  </si>
+  <si>
+    <t>GIDA 358</t>
   </si>
   <si>
     <t>MAK 364</t>
   </si>
   <si>
-    <t>GIDA 354</t>
-  </si>
-  <si>
-    <t>JEO 312</t>
-  </si>
-  <si>
-    <t>CSE 408</t>
-  </si>
-  <si>
-    <t>İNM 214</t>
-  </si>
-  <si>
-    <t>ÇEV 416</t>
-  </si>
-  <si>
-    <t>MAK 208</t>
-  </si>
-  <si>
-    <t>CSE 308</t>
-  </si>
-  <si>
-    <t>CSE 358</t>
-  </si>
-  <si>
-    <t>EEM 208</t>
-  </si>
-  <si>
-    <t>GIDA 353</t>
-  </si>
-  <si>
-    <t>MAK 402</t>
-  </si>
-  <si>
-    <t>İNM 212</t>
-  </si>
-  <si>
-    <t>GIDA 238</t>
-  </si>
-  <si>
-    <t>JEO 404</t>
-  </si>
-  <si>
-    <t>EEE 484</t>
-  </si>
-  <si>
-    <t>İNM 106</t>
-  </si>
-  <si>
-    <t>EEE 496</t>
-  </si>
-  <si>
-    <t>ÇEV 210</t>
-  </si>
-  <si>
-    <t>MAK 210</t>
-  </si>
-  <si>
-    <t>CSE 328</t>
-  </si>
-  <si>
-    <t>EEM 210</t>
-  </si>
-  <si>
-    <t>EEM 352</t>
-  </si>
-  <si>
-    <t>MAK 426</t>
-  </si>
-  <si>
-    <t>İNM 466</t>
-  </si>
-  <si>
     <t>EEE 440</t>
   </si>
   <si>
-    <t>GIDA 450</t>
+    <t>GIDA 454</t>
   </si>
   <si>
     <t>JEO 302</t>
   </si>
   <si>
-    <t>İNM 204</t>
-  </si>
-  <si>
-    <t>ÇEV 306</t>
-  </si>
-  <si>
-    <t>CSE 336</t>
-  </si>
-  <si>
-    <t>MAK 308</t>
-  </si>
-  <si>
-    <t>CSE 472</t>
-  </si>
-  <si>
-    <t>MAK 458</t>
-  </si>
-  <si>
-    <t>EEM 306</t>
-  </si>
-  <si>
-    <t>GIDA 222</t>
-  </si>
-  <si>
-    <t>JEO 408</t>
-  </si>
-  <si>
-    <t>İNM 452</t>
-  </si>
-  <si>
-    <t>ÇEV 162</t>
-  </si>
-  <si>
-    <t>CSE 460</t>
-  </si>
-  <si>
-    <t>MAK 110</t>
-  </si>
-  <si>
-    <t>İNM 356</t>
-  </si>
-  <si>
-    <t>GIDA 454</t>
-  </si>
-  <si>
     <t>İNM 110</t>
   </si>
   <si>
+    <t>ÇEV 254</t>
+  </si>
+  <si>
+    <t>GIDA 356</t>
+  </si>
+  <si>
+    <t>GIDA 216</t>
+  </si>
+  <si>
+    <t>JEO 210</t>
+  </si>
+  <si>
+    <t>İNM 360</t>
+  </si>
+  <si>
+    <t>MAK 212</t>
+  </si>
+  <si>
+    <t>İNM 302</t>
+  </si>
+  <si>
     <t>ÇEV 160</t>
   </si>
   <si>
+    <t>CSE 440</t>
+  </si>
+  <si>
+    <t>EEM 318</t>
+  </si>
+  <si>
+    <t>GIDA 234</t>
+  </si>
+  <si>
+    <t>JEO 330</t>
+  </si>
+  <si>
+    <t>MAK 306</t>
+  </si>
+  <si>
+    <t>İNM 208</t>
+  </si>
+  <si>
     <t>GIDA 254</t>
   </si>
   <si>
+    <t>MAK 466</t>
+  </si>
+  <si>
+    <t>EEM 308</t>
+  </si>
+  <si>
+    <t>JEO 432</t>
+  </si>
+  <si>
+    <t>İNM 104</t>
+  </si>
+  <si>
+    <t>MTH 404</t>
+  </si>
+  <si>
+    <t>GIDA 260</t>
+  </si>
+  <si>
     <t>MAK 418</t>
   </si>
   <si>
-    <t>GIDA 216</t>
+    <t>EEE 430</t>
+  </si>
+  <si>
+    <t>GIDA 350</t>
   </si>
   <si>
     <t>JEO 102</t>
   </si>
   <si>
-    <t>İNM 360</t>
-  </si>
-  <si>
-    <t>İNM 302</t>
-  </si>
-  <si>
-    <t>MAK 212</t>
-  </si>
-  <si>
-    <t>ÇEV 254</t>
-  </si>
-  <si>
-    <t>CSE 440</t>
-  </si>
-  <si>
-    <t>GIDA 356</t>
-  </si>
-  <si>
-    <t>MAK 466</t>
-  </si>
-  <si>
-    <t>EEE 430</t>
-  </si>
-  <si>
-    <t>GIDA 234</t>
-  </si>
-  <si>
-    <t>JEO 210</t>
-  </si>
-  <si>
-    <t>MAK 306</t>
-  </si>
-  <si>
-    <t>İNM 208</t>
-  </si>
-  <si>
-    <t>GIDA 358</t>
-  </si>
-  <si>
-    <t>EEM 308</t>
-  </si>
-  <si>
-    <t>GIDA 350</t>
-  </si>
-  <si>
-    <t>JEO 330</t>
-  </si>
-  <si>
-    <t>İNM 104</t>
-  </si>
-  <si>
-    <t>MTH 404</t>
-  </si>
-  <si>
-    <t>EEM 318</t>
-  </si>
-  <si>
-    <t>JEO 432</t>
+    <t>İNM 462</t>
+  </si>
+  <si>
+    <t>EEE 490</t>
+  </si>
+  <si>
+    <t>GIDA 102</t>
+  </si>
+  <si>
+    <t>JEO 202</t>
+  </si>
+  <si>
+    <t>GIDA 464</t>
+  </si>
+  <si>
+    <t>MAK 454</t>
+  </si>
+  <si>
+    <t>İNM 476</t>
+  </si>
+  <si>
+    <t>EEE 422</t>
+  </si>
+  <si>
+    <t>GIDA 236</t>
+  </si>
+  <si>
+    <t>JEO 308</t>
+  </si>
+  <si>
+    <t>GIDA 388</t>
+  </si>
+  <si>
+    <t>İNM 308</t>
   </si>
   <si>
     <t>MAK 420</t>
   </si>
   <si>
-    <t>EEE 490</t>
-  </si>
-  <si>
-    <t>GIDA 102</t>
-  </si>
-  <si>
-    <t>JEO 202</t>
-  </si>
-  <si>
-    <t>GIDA 260</t>
-  </si>
-  <si>
-    <t>MAK 454</t>
-  </si>
-  <si>
-    <t>İNM 462</t>
-  </si>
-  <si>
-    <t>GIDA 236</t>
-  </si>
-  <si>
-    <t>JEO 308</t>
+    <t>GIDA 324</t>
+  </si>
+  <si>
+    <t>JEO 314</t>
   </si>
   <si>
     <t>İNM 306</t>
   </si>
   <si>
-    <t>GIDA 464</t>
-  </si>
-  <si>
-    <t>İNM 476</t>
-  </si>
-  <si>
-    <t>GIDA 388</t>
-  </si>
-  <si>
-    <t>JEO 314</t>
-  </si>
-  <si>
-    <t>İNM 308</t>
-  </si>
-  <si>
     <t>GIDA 360</t>
   </si>
   <si>
-    <t>EEE 422</t>
+    <t>MAK 412</t>
+  </si>
+  <si>
+    <t>İNM 480</t>
   </si>
   <si>
     <t>GIDA 224</t>
@@ -712,37 +721,28 @@
     <t>GIDA 406</t>
   </si>
   <si>
-    <t>MAK 412</t>
-  </si>
-  <si>
-    <t>GIDA 324</t>
+    <t>MAK 434</t>
+  </si>
+  <si>
+    <t>İNM 362</t>
   </si>
   <si>
     <t>MAK 422</t>
   </si>
   <si>
-    <t>İNM 362</t>
-  </si>
-  <si>
-    <t>MAK 434</t>
-  </si>
-  <si>
-    <t>İNM 480</t>
+    <t>EEE 498</t>
   </si>
   <si>
     <t>EEE 448</t>
   </si>
   <si>
-    <t>EEE 498</t>
-  </si>
-  <si>
     <t>GIDA 456</t>
   </si>
   <si>
+    <t>GIDA 312</t>
+  </si>
+  <si>
     <t>MAK 456</t>
-  </si>
-  <si>
-    <t>GIDA 312</t>
   </si>
   <si>
     <t>GIDA 468</t>
@@ -1215,19 +1215,19 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
         <v>42</v>
       </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H2" t="s">
         <v>118</v>
@@ -1236,70 +1236,70 @@
         <v>131</v>
       </c>
       <c r="J2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="Q2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R2" t="s">
+        <v>209</v>
+      </c>
+      <c r="S2" t="s">
         <v>191</v>
       </c>
-      <c r="S2" t="s">
-        <v>201</v>
-      </c>
       <c r="T2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U2" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="V2" t="s">
-        <v>228</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X2" t="s">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="Y2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AA2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AB2" t="s">
         <v>240</v>
       </c>
       <c r="AC2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="AD2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE2" t="s">
         <v>233</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>242</v>
       </c>
       <c r="AF2" t="s">
         <v>243</v>
@@ -1313,91 +1313,91 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s">
         <v>132</v>
       </c>
       <c r="J3" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L3" t="s">
         <v>167</v>
       </c>
       <c r="M3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="O3" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="s">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="R3" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="S3" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="T3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U3" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="V3" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="W3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Y3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AB3" t="s">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="AC3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="AD3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AE3" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1411,85 +1411,85 @@
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" t="s">
         <v>78</v>
       </c>
-      <c r="G4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M4" t="s">
-        <v>169</v>
-      </c>
       <c r="N4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O4" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="P4" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T4" t="s">
         <v>211</v>
       </c>
       <c r="U4" t="s">
-        <v>48</v>
+        <v>221</v>
       </c>
       <c r="V4" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="W4" t="s">
-        <v>229</v>
+        <v>140</v>
       </c>
       <c r="X4" t="s">
         <v>127</v>
       </c>
       <c r="Y4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Z4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC4" t="s">
         <v>165</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AD4" t="s">
         <v>239</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1500,85 +1500,85 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
         <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="H5" t="s">
         <v>119</v>
       </c>
       <c r="I5" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="K5" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="L5" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="M5" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="N5" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="O5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q5" t="s">
         <v>193</v>
       </c>
       <c r="R5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S5" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="T5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="U5" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="V5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W5" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="X5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y5" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="Z5" t="s">
-        <v>54</v>
+        <v>202</v>
       </c>
       <c r="AA5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AB5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC5" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1589,76 +1589,76 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" t="s">
         <v>78</v>
       </c>
-      <c r="F6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" t="s">
-        <v>124</v>
-      </c>
-      <c r="L6" t="s">
-        <v>169</v>
-      </c>
       <c r="M6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N6" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="O6" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Q6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R6" t="s">
         <v>211</v>
       </c>
       <c r="S6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T6" t="s">
-        <v>48</v>
+        <v>221</v>
       </c>
       <c r="U6" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="V6" t="s">
-        <v>229</v>
+        <v>140</v>
       </c>
       <c r="W6" t="s">
         <v>127</v>
       </c>
       <c r="X6" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y6" t="s">
         <v>165</v>
       </c>
-      <c r="Y6" t="s">
-        <v>238</v>
-      </c>
       <c r="Z6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1669,37 +1669,37 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
         <v>42</v>
       </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I7" t="s">
         <v>131</v>
       </c>
       <c r="J7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="N7" t="s">
         <v>186</v>
@@ -1708,25 +1708,25 @@
         <v>191</v>
       </c>
       <c r="P7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q7" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="R7" t="s">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="S7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="U7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="W7" t="s">
         <v>233</v>
@@ -1740,19 +1740,19 @@
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H8" t="s">
         <v>121</v>
@@ -1761,43 +1761,43 @@
         <v>134</v>
       </c>
       <c r="J8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N8" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="O8" t="s">
         <v>192</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="S8" t="s">
+        <v>217</v>
+      </c>
+      <c r="T8" t="s">
+        <v>223</v>
+      </c>
+      <c r="U8" t="s">
         <v>216</v>
       </c>
-      <c r="T8" t="s">
-        <v>221</v>
-      </c>
-      <c r="U8" t="s">
-        <v>226</v>
-      </c>
       <c r="V8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -1808,64 +1808,64 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O9" t="s">
         <v>193</v>
       </c>
       <c r="P9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="S9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T9" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="U9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="V9" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -1879,46 +1879,46 @@
         <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I10" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="K10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M10" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O10" t="s">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="Q10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -1929,49 +1929,49 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
         <v>94</v>
       </c>
       <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
         <v>85</v>
-      </c>
-      <c r="H11" t="s">
-        <v>74</v>
       </c>
       <c r="I11" t="s">
         <v>86</v>
       </c>
       <c r="J11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N11" t="s">
         <v>90</v>
       </c>
       <c r="O11" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="P11" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="Q11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1982,49 +1982,49 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" t="s">
         <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I12" t="s">
         <v>126</v>
       </c>
       <c r="J12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -2035,46 +2035,46 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
         <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
         <v>96</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -2085,46 +2085,46 @@
         <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
       </c>
       <c r="G14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" t="s">
         <v>78</v>
       </c>
-      <c r="H14" t="s">
-        <v>124</v>
-      </c>
-      <c r="I14" t="s">
-        <v>75</v>
-      </c>
       <c r="J14" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N14" t="s">
         <v>127</v>
       </c>
       <c r="O14" t="s">
+        <v>153</v>
+      </c>
+      <c r="P14" t="s">
         <v>165</v>
-      </c>
-      <c r="P14" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -2135,40 +2135,40 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
         <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
         <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H15" t="s">
         <v>125</v>
       </c>
       <c r="I15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O15" t="s">
         <v>196</v>
@@ -2182,40 +2182,40 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
         <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
         <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
         <v>89</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L16" t="s">
+        <v>172</v>
+      </c>
+      <c r="M16" t="s">
+        <v>181</v>
+      </c>
+      <c r="N16" t="s">
         <v>174</v>
-      </c>
-      <c r="M16" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" t="s">
-        <v>176</v>
       </c>
       <c r="O16" t="s">
         <v>197</v>
@@ -2229,37 +2229,37 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
         <v>95</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
         <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2267,37 +2267,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
         <v>89</v>
       </c>
-      <c r="G18" t="s">
-        <v>113</v>
-      </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -2305,10 +2305,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
@@ -2317,25 +2317,25 @@
         <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="G19" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s">
         <v>90</v>
       </c>
       <c r="K19" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -2343,34 +2343,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s">
         <v>90</v>
       </c>
       <c r="J20" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2378,31 +2378,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" t="s">
         <v>59</v>
       </c>
-      <c r="D21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" t="s">
-        <v>40</v>
-      </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s">
         <v>165</v>
@@ -2413,34 +2413,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J22" t="s">
+        <v>130</v>
+      </c>
+      <c r="K22" t="s">
         <v>129</v>
-      </c>
-      <c r="K22" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -2448,19 +2448,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G23" t="s">
         <v>115</v>
@@ -2469,7 +2469,7 @@
         <v>127</v>
       </c>
       <c r="I23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J23" t="s">
         <v>153</v>
@@ -2483,19 +2483,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
         <v>116</v>
@@ -2504,7 +2504,7 @@
         <v>128</v>
       </c>
       <c r="I24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2512,28 +2512,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s">
         <v>129</v>
       </c>
       <c r="I25" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -2541,19 +2541,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s">
         <v>117</v>
@@ -2567,22 +2567,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
         <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s">
         <v>130</v>
@@ -2593,16 +2593,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
         <v>89</v>
@@ -2616,19 +2616,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
         <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2636,7 +2636,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
